--- a/tabtools/qa/baseline/workbooks/crosstab_2x2_chi2.xlsx
+++ b/tabtools/qa/baseline/workbooks/crosstab_2x2_chi2.xlsx
@@ -64,7 +64,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="124">
+  <fonts count="140">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -494,6 +494,70 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -588,7 +652,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="91">
+  <borders count="107">
     <border>
       <left/>
       <right/>
@@ -1132,6 +1196,118 @@
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -1200,7 +1376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1542,11 +1718,75 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1559,11 +1799,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="86" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="87" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" style="88" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" style="89" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" style="90" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="102" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="103" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="104" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="105" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="106" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1655,22 +1895,23 @@
       <c r="A6" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="77" t="s">
+      <c r="E6" s="101" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B6:E6"/>
   </mergeCells>
 </worksheet>
 </file>